--- a/data/raw/exogenous/anex-IPP-historicos-jun2025.xlsx
+++ b/data/raw/exogenous/anex-IPP-historicos-jun2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DANE\Documents\3IPP_versión 1.0\Datos\2025\Junio_2025\salidas\Enviados\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Camilo\Dev\maestria-trabajo-integrador\data\raw\exogenous\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8496A89A-5588-489A-B813-A2096AB3CE53}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19A81FF9-AE19-4FF5-80BF-669FFDDE65D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="IPP Histórico" sheetId="1" r:id="rId1"/>
@@ -143,7 +143,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="368" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="70">
   <si>
     <t>(Base: Diciembre  2014=100)</t>
   </si>
@@ -445,10 +445,10 @@
     <t>Nota: La diferencia en el cálculo de las variables, obedece al sistema de aproximación en el nivel de dígitos trabajados en el índice.</t>
   </si>
   <si>
-    <t>Junio (pr*)</t>
+    <t>Actualizado el 4 de Julio de 2025</t>
   </si>
   <si>
-    <t>Actualizado el 4 de Julio de 2025</t>
+    <t>Julio (pr*)</t>
   </si>
 </sst>
 </file>
@@ -700,7 +700,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -818,6 +818,30 @@
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -836,32 +860,35 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="2" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="1" fillId="9" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="1" fillId="8" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="2" fontId="1" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1420,7 +1447,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O327"/>
+  <dimension ref="A1:O328"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.5703125" customWidth="1"/>
@@ -1441,75 +1468,75 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:15" ht="70.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C1" s="41"/>
-      <c r="D1" s="41"/>
-      <c r="E1" s="41"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="41"/>
-      <c r="J1" s="41"/>
-      <c r="K1" s="41"/>
-      <c r="L1" s="41"/>
-      <c r="M1" s="41"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
+      <c r="M1" s="49"/>
     </row>
     <row r="2" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="30"/>
       <c r="B2" s="30"/>
-      <c r="C2" s="42" t="s">
+      <c r="C2" s="50" t="s">
         <v>20</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="42"/>
-      <c r="H2" s="42"/>
-      <c r="I2" s="42"/>
-      <c r="J2" s="42"/>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
-      <c r="M2" s="42"/>
+      <c r="D2" s="50"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="50"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
     </row>
     <row r="3" spans="1:15" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B3" s="30"/>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="43"/>
-      <c r="E3" s="43"/>
-      <c r="F3" s="43"/>
-      <c r="G3" s="43"/>
-      <c r="H3" s="43"/>
-      <c r="I3" s="43"/>
-      <c r="J3" s="43"/>
-      <c r="K3" s="43"/>
-      <c r="L3" s="43"/>
-      <c r="M3" s="43"/>
+      <c r="D3" s="51"/>
+      <c r="E3" s="51"/>
+      <c r="F3" s="51"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="51"/>
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="51"/>
+      <c r="M3" s="51"/>
     </row>
     <row r="4" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="23"/>
       <c r="B4" s="23"/>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="54" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="46"/>
-      <c r="E4" s="46"/>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46" t="s">
+      <c r="D4" s="54"/>
+      <c r="E4" s="54"/>
+      <c r="F4" s="54"/>
+      <c r="G4" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="H4" s="46"/>
-      <c r="I4" s="46"/>
-      <c r="J4" s="46"/>
-      <c r="K4" s="46" t="s">
+      <c r="H4" s="54"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54" t="s">
         <v>11</v>
       </c>
-      <c r="L4" s="46"/>
-      <c r="M4" s="46"/>
+      <c r="L4" s="54"/>
+      <c r="M4" s="54"/>
     </row>
     <row r="5" spans="1:15" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="44"/>
-      <c r="B5" s="45"/>
+      <c r="A5" s="52"/>
+      <c r="B5" s="53"/>
       <c r="C5" s="5" t="s">
         <v>1</v>
       </c>
@@ -14165,37 +14192,37 @@
       <c r="B316" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="C316" s="49">
+      <c r="C316" s="41">
         <v>186.51</v>
       </c>
-      <c r="D316" s="49">
+      <c r="D316" s="41">
         <v>297.35000000000002</v>
       </c>
-      <c r="E316" s="49">
+      <c r="E316" s="41">
         <v>133.72999999999999</v>
       </c>
-      <c r="F316" s="49">
+      <c r="F316" s="41">
         <v>178.71</v>
       </c>
-      <c r="G316" s="50">
+      <c r="G316" s="42">
         <v>185.55</v>
       </c>
-      <c r="H316" s="49">
+      <c r="H316" s="41">
         <v>299.27999999999997</v>
       </c>
-      <c r="I316" s="49">
+      <c r="I316" s="41">
         <v>178.57</v>
       </c>
-      <c r="J316" s="49">
+      <c r="J316" s="41">
         <v>167.59</v>
       </c>
-      <c r="K316" s="50">
+      <c r="K316" s="42">
         <v>195.57</v>
       </c>
-      <c r="L316" s="49">
+      <c r="L316" s="41">
         <v>161.79</v>
       </c>
-      <c r="M316" s="49">
+      <c r="M316" s="41">
         <v>163.33000000000001</v>
       </c>
       <c r="N316" s="40"/>
@@ -14207,101 +14234,125 @@
       <c r="B317" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="C317" s="51">
+      <c r="C317" s="43">
         <v>184.42</v>
       </c>
-      <c r="D317" s="51">
+      <c r="D317" s="43">
         <v>288.44</v>
       </c>
-      <c r="E317" s="51">
+      <c r="E317" s="43">
         <v>129.55000000000001</v>
       </c>
-      <c r="F317" s="51">
+      <c r="F317" s="43">
         <v>178.59</v>
       </c>
-      <c r="G317" s="52">
+      <c r="G317" s="44">
         <v>183.75</v>
       </c>
-      <c r="H317" s="51">
+      <c r="H317" s="43">
         <v>290.23</v>
       </c>
-      <c r="I317" s="51">
+      <c r="I317" s="43">
         <v>172.64</v>
       </c>
-      <c r="J317" s="51">
+      <c r="J317" s="43">
         <v>167.15</v>
       </c>
-      <c r="K317" s="52">
+      <c r="K317" s="44">
         <v>193.6</v>
       </c>
-      <c r="L317" s="51">
+      <c r="L317" s="43">
         <v>160.38</v>
       </c>
-      <c r="M317" s="51">
+      <c r="M317" s="43">
         <v>160.94999999999999</v>
       </c>
       <c r="N317" s="40"/>
     </row>
     <row r="318" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A318" s="37" t="s">
+      <c r="A318" s="36"/>
+      <c r="B318" s="60" t="s">
+        <v>13</v>
+      </c>
+      <c r="C318" s="61">
+        <v>183.91</v>
+      </c>
+      <c r="D318" s="61">
+        <v>281.14999999999998</v>
+      </c>
+      <c r="E318" s="61">
+        <v>134.61000000000001</v>
+      </c>
+      <c r="F318" s="61">
+        <v>177.9</v>
+      </c>
+      <c r="G318" s="56">
+        <v>182.59</v>
+      </c>
+      <c r="H318" s="61">
+        <v>283.39999999999998</v>
+      </c>
+      <c r="I318" s="61">
+        <v>178.06</v>
+      </c>
+      <c r="J318" s="61">
+        <v>166.58</v>
+      </c>
+      <c r="K318" s="56">
+        <v>192.61</v>
+      </c>
+      <c r="L318" s="61">
+        <v>158.83000000000001</v>
+      </c>
+      <c r="M318" s="64">
+        <v>161.66999999999999</v>
+      </c>
+      <c r="N318" s="63"/>
+    </row>
+    <row r="319" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A319" s="55" t="s">
         <v>60</v>
       </c>
-      <c r="B318" s="38" t="s">
-        <v>68</v>
-      </c>
-      <c r="C318" s="49">
-        <v>183.91</v>
-      </c>
-      <c r="D318" s="49">
-        <v>281.14999999999998</v>
-      </c>
-      <c r="E318" s="49">
-        <v>134.61000000000001</v>
-      </c>
-      <c r="F318" s="49">
-        <v>177.9</v>
-      </c>
-      <c r="G318" s="50">
-        <v>182.59</v>
-      </c>
-      <c r="H318" s="49">
-        <v>283.39999999999998</v>
-      </c>
-      <c r="I318" s="49">
-        <v>178.06</v>
-      </c>
-      <c r="J318" s="49">
-        <v>166.58</v>
-      </c>
-      <c r="K318" s="50">
-        <v>192.61</v>
-      </c>
-      <c r="L318" s="49">
-        <v>158.83000000000001</v>
-      </c>
-      <c r="M318" s="53">
-        <v>161.66999999999999</v>
-      </c>
-      <c r="N318" s="40"/>
-    </row>
-    <row r="319" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A319" s="16"/>
-      <c r="B319" s="16"/>
-      <c r="C319" s="16"/>
-      <c r="D319" s="16"/>
-      <c r="E319" s="16"/>
-      <c r="F319" s="16"/>
-      <c r="G319" s="16"/>
-      <c r="H319" s="16"/>
-      <c r="I319" s="16"/>
-      <c r="J319" s="16"/>
-      <c r="K319" s="16"/>
-      <c r="L319" s="16"/>
+      <c r="B319" s="58" t="s">
+        <v>69</v>
+      </c>
+      <c r="C319" s="59">
+        <v>184.62</v>
+      </c>
+      <c r="D319" s="59">
+        <v>291.47000000000003</v>
+      </c>
+      <c r="E319" s="59">
+        <v>133.97999999999999</v>
+      </c>
+      <c r="F319" s="59">
+        <v>177.03</v>
+      </c>
+      <c r="G319" s="57">
+        <v>183.74</v>
+      </c>
+      <c r="H319" s="59">
+        <v>293.93</v>
+      </c>
+      <c r="I319" s="59">
+        <v>181.1</v>
+      </c>
+      <c r="J319" s="59">
+        <v>166.13</v>
+      </c>
+      <c r="K319" s="57">
+        <v>194.73</v>
+      </c>
+      <c r="L319" s="59">
+        <v>157.68</v>
+      </c>
+      <c r="M319" s="62">
+        <v>158.76</v>
+      </c>
+      <c r="N319" s="40"/>
     </row>
     <row r="320" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A320" s="16" t="s">
-        <v>61</v>
-      </c>
+      <c r="A320" s="16"/>
       <c r="B320" s="16"/>
       <c r="C320" s="16"/>
       <c r="D320" s="16"/>
@@ -14313,120 +14364,118 @@
       <c r="J320" s="16"/>
       <c r="K320" s="16"/>
       <c r="L320" s="16"/>
-      <c r="M320" s="16"/>
-      <c r="N320" s="40"/>
-    </row>
-    <row r="321" spans="1:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A321" s="47" t="s">
+    </row>
+    <row r="321" spans="1:14" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A321" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="B321" s="16"/>
+      <c r="C321" s="16"/>
+      <c r="D321" s="16"/>
+      <c r="E321" s="16"/>
+      <c r="F321" s="16"/>
+      <c r="G321" s="16"/>
+      <c r="H321" s="16"/>
+      <c r="I321" s="16"/>
+      <c r="J321" s="16"/>
+      <c r="K321" s="16"/>
+      <c r="L321" s="16"/>
+      <c r="M321" s="16"/>
+      <c r="N321" s="40"/>
+    </row>
+    <row r="322" spans="1:14" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A322" s="48" t="s">
         <v>62</v>
       </c>
-      <c r="B321" s="47"/>
-      <c r="C321" s="47"/>
-      <c r="D321" s="47"/>
-      <c r="E321" s="47"/>
-      <c r="F321" s="47"/>
-      <c r="G321" s="47"/>
-      <c r="H321" s="47"/>
-      <c r="I321" s="47"/>
-      <c r="J321" s="47"/>
-      <c r="K321" s="47"/>
-      <c r="L321" s="47"/>
-      <c r="M321" s="47"/>
-      <c r="N321" s="40"/>
-    </row>
-    <row r="322" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A322" s="54" t="s">
+      <c r="B322" s="48"/>
+      <c r="C322" s="48"/>
+      <c r="D322" s="48"/>
+      <c r="E322" s="48"/>
+      <c r="F322" s="48"/>
+      <c r="G322" s="48"/>
+      <c r="H322" s="48"/>
+      <c r="I322" s="48"/>
+      <c r="J322" s="48"/>
+      <c r="K322" s="48"/>
+      <c r="L322" s="48"/>
+      <c r="M322" s="48"/>
+      <c r="N322" s="40"/>
+    </row>
+    <row r="323" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A323" s="46" t="s">
         <v>63</v>
       </c>
-      <c r="B322" s="54"/>
-      <c r="C322" s="54"/>
-      <c r="D322" s="54"/>
-      <c r="E322" s="54"/>
-      <c r="F322" s="54"/>
-      <c r="G322" s="54"/>
-      <c r="H322" s="54"/>
-      <c r="I322" s="54"/>
-      <c r="J322" s="54"/>
-      <c r="K322" s="54"/>
-      <c r="L322" s="54"/>
-      <c r="M322" s="55"/>
-      <c r="N322" s="9"/>
-    </row>
-    <row r="323" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A323" s="47" t="s">
-        <v>64</v>
-      </c>
-      <c r="B323" s="47"/>
-      <c r="C323" s="47"/>
-      <c r="D323" s="47"/>
-      <c r="E323" s="47"/>
-      <c r="F323" s="47"/>
-      <c r="G323" s="47"/>
-      <c r="H323" s="47"/>
-      <c r="I323" s="47"/>
-      <c r="J323" s="47"/>
-      <c r="K323" s="47"/>
-      <c r="L323" s="47"/>
+      <c r="B323" s="46"/>
+      <c r="C323" s="46"/>
+      <c r="D323" s="46"/>
+      <c r="E323" s="46"/>
+      <c r="F323" s="46"/>
+      <c r="G323" s="46"/>
+      <c r="H323" s="46"/>
+      <c r="I323" s="46"/>
+      <c r="J323" s="46"/>
+      <c r="K323" s="46"/>
+      <c r="L323" s="46"/>
       <c r="M323" s="47"/>
       <c r="N323" s="9"/>
     </row>
     <row r="324" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A324" s="47" t="s">
+      <c r="A324" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="B324" s="48"/>
+      <c r="C324" s="48"/>
+      <c r="D324" s="48"/>
+      <c r="E324" s="48"/>
+      <c r="F324" s="48"/>
+      <c r="G324" s="48"/>
+      <c r="H324" s="48"/>
+      <c r="I324" s="48"/>
+      <c r="J324" s="48"/>
+      <c r="K324" s="48"/>
+      <c r="L324" s="48"/>
+      <c r="M324" s="48"/>
+      <c r="N324" s="9"/>
+    </row>
+    <row r="325" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A325" s="48" t="s">
         <v>65</v>
       </c>
-      <c r="B324" s="47"/>
-      <c r="C324" s="47"/>
-      <c r="D324" s="47"/>
-      <c r="E324" s="47"/>
-      <c r="F324" s="47"/>
-      <c r="G324" s="47"/>
-      <c r="H324" s="47"/>
-      <c r="I324" s="47"/>
-      <c r="J324" s="47"/>
-      <c r="K324" s="47"/>
-      <c r="L324" s="47"/>
-      <c r="M324" s="47"/>
-      <c r="N324" s="9"/>
-    </row>
-    <row r="325" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A325" s="47" t="s">
+      <c r="B325" s="48"/>
+      <c r="C325" s="48"/>
+      <c r="D325" s="48"/>
+      <c r="E325" s="48"/>
+      <c r="F325" s="48"/>
+      <c r="G325" s="48"/>
+      <c r="H325" s="48"/>
+      <c r="I325" s="48"/>
+      <c r="J325" s="48"/>
+      <c r="K325" s="48"/>
+      <c r="L325" s="48"/>
+      <c r="M325" s="48"/>
+      <c r="N325" s="9"/>
+    </row>
+    <row r="326" spans="1:14" ht="26.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A326" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="B325" s="47"/>
-      <c r="C325" s="47"/>
-      <c r="D325" s="47"/>
-      <c r="E325" s="47"/>
-      <c r="F325" s="47"/>
-      <c r="G325" s="47"/>
-      <c r="H325" s="47"/>
-      <c r="I325" s="47"/>
-      <c r="J325" s="47"/>
-      <c r="K325" s="47"/>
-      <c r="L325" s="47"/>
-      <c r="M325" s="47"/>
-      <c r="N325" s="40"/>
-    </row>
-    <row r="326" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A326" s="47" t="s">
-        <v>67</v>
-      </c>
-      <c r="B326" s="47"/>
-      <c r="C326" s="47"/>
-      <c r="D326" s="47"/>
-      <c r="E326" s="47"/>
-      <c r="F326" s="47"/>
-      <c r="G326" s="47"/>
-      <c r="H326" s="47"/>
-      <c r="I326" s="47"/>
-      <c r="J326" s="47"/>
-      <c r="K326" s="47"/>
-      <c r="L326" s="47"/>
-      <c r="M326" s="47"/>
+      <c r="B326" s="48"/>
+      <c r="C326" s="48"/>
+      <c r="D326" s="48"/>
+      <c r="E326" s="48"/>
+      <c r="F326" s="48"/>
+      <c r="G326" s="48"/>
+      <c r="H326" s="48"/>
+      <c r="I326" s="48"/>
+      <c r="J326" s="48"/>
+      <c r="K326" s="48"/>
+      <c r="L326" s="48"/>
+      <c r="M326" s="48"/>
       <c r="N326" s="40"/>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A327" s="48" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B327" s="48"/>
       <c r="C327" s="48"/>
@@ -14442,15 +14491,26 @@
       <c r="M327" s="48"/>
       <c r="N327" s="40"/>
     </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A328" s="45" t="s">
+        <v>68</v>
+      </c>
+      <c r="B328" s="45"/>
+      <c r="C328" s="45"/>
+      <c r="D328" s="45"/>
+      <c r="E328" s="45"/>
+      <c r="F328" s="45"/>
+      <c r="G328" s="45"/>
+      <c r="H328" s="45"/>
+      <c r="I328" s="45"/>
+      <c r="J328" s="45"/>
+      <c r="K328" s="45"/>
+      <c r="L328" s="45"/>
+      <c r="M328" s="45"/>
+      <c r="N328" s="40"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
-    <mergeCell ref="A327:M327"/>
-    <mergeCell ref="A322:M322"/>
-    <mergeCell ref="A321:M321"/>
-    <mergeCell ref="A323:M323"/>
-    <mergeCell ref="A324:M324"/>
-    <mergeCell ref="A325:M325"/>
-    <mergeCell ref="A326:M326"/>
     <mergeCell ref="C1:M1"/>
     <mergeCell ref="C2:M2"/>
     <mergeCell ref="C3:M3"/>
@@ -14458,6 +14518,13 @@
     <mergeCell ref="G4:J4"/>
     <mergeCell ref="C4:F4"/>
     <mergeCell ref="K4:M4"/>
+    <mergeCell ref="A328:M328"/>
+    <mergeCell ref="A323:M323"/>
+    <mergeCell ref="A322:M322"/>
+    <mergeCell ref="A324:M324"/>
+    <mergeCell ref="A325:M325"/>
+    <mergeCell ref="A326:M326"/>
+    <mergeCell ref="A327:M327"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="0.21" bottom="0.36" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
